--- a/data_extactor/batch_10_fa/trimmed/batch_0054_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0054_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | حقوق و امور حکومتی | آموزش و تدریس</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | دید نزدیک | دید دور | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | بینایی دور | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | مأموران گشت پلیس و کلانتری | کارشناسان پیشگیری از سرقت و کسری کالا در فروشگاه | نگهبانان و مأموران حراست | مدیران حراست و انتظامات</t>
+          <t>سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول پلیس و کارآگاهان | ماموران گشت پلیس و کلانتری | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | نگهبانان و ماموران حراست | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | حقوق و امور حکومتی | امور اداری و منابع انسانی | آموزش و تدریس</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول کارکنان حراست و انتظامات | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | نگهبانان و مأموران حراست | مأموران گشت پلیس و کلانتری | مدیران حراست و انتظامات</t>
+          <t>سرپرستان رده‌اول کارکنان حراست و انتظامات | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | ماموران گشت پلیس و کلانتری | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ساختمان و سازه | مکانیک | پزشکی و دندان‌پزشکی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | ساختمان و ساخت‌وساز | مکانیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | ثبات دست و بازو | قدرت ایستا | استقامت بدنی | قدرت تنه</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | ثبات دست و بازو | قدرت ایستا | استقامت | قدرت تنه</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌های فوریت‌های پزشکی | بازرسان و کارشناسان بررسی علل حریق | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | بازرسان و کارشناسان پیشگیری از حریق جنگل | امدادگران و تکنسین‌های ارشد فوریت‌های پزشکی | نگهبانان و مأموران حراست</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌های فوریت‌های پزشکی | بازرسان و کارشناسان بررسی علل حریق | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | بازرسان و کارشناسان پیشگیری از حریق جنگل | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | نگهبانان و ماموران حراست</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | ساختمان و سازه | حقوق و امور حکومتی | آموزش و تدریس | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | قانون و دولت | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازرسان ساختمان و سازه | مهندسان ایمنی و حفاظت در برابر حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | بازرسان و کارشناسان پیشگیری از حریق جنگل | کارشناسان بهداشت حرفه‌ای و ایمنی کار | نصابان سیستم‌های اعلام و اطفای حریق و دزدگیر</t>
+          <t>بازرسان ساخت‌وساز و ساختمان | مهندسان پیشگیری و حفاظت از حریق | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | بازرسان و کارشناسان پیشگیری از حریق جنگل | کارشناسان بهداشت حرفه‌ای و ایمنی کار | نصاب سیستم‌های اعلام سرقت و حریق</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | آموزش و تدریس | ایمنی و امنیت عمومی | حقوق و امور حکومتی | ترابری و حمل‌ونقل | جغرافیا</t>
+          <t>مدیریت و اداره | آموزش و پرورش | ایمنی و امنیت عمومی | قانون و دولت | حمل و نقل | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | درک کتبی | دید دور | استدلال استقرایی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | درک کتبی | بینایی دور | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بازرسان و کارشناسان بررسی علل حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان کشاورزی، صیادی و جنگل‌داری | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران حفاظت از جنگل و منابع طبیعی | جنگل‌داران و کارشناسان جنگل | مدیران مراتع و آبخیزداری</t>
+          <t>بازرسان و کارشناسان بررسی علل حریق | آتش‌نشانان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | مدیران و کارشناسان مدیریت مراتع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و امور حکومتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مأموران زندان و بازداشتگاه | کارمندان دادگاه، شهرداری و صدور مجوزها | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول کارکنان حراست و انتظامات | قضات، دادرسان و مأموران دادرسی دادگاه | مأموران گشت پلیس و کلانتری | نگهبانان و مأموران حراست</t>
+          <t>مأموران زندان و بازداشتگاه | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول کارکنان حراست و انتظامات | قضات دادگاه و دادیاران | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و امور حکومتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | روان‌شناسی | آموزش و تدریس</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | روان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مأموران انتظامات و حفاظت دادگاه | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول کارکنان حراست و انتظامات | مأموران گشت پلیس و کلانتری | مأموران آزادی مشروط و مددکاران اقدامات تأمینی و تربیتی | نگهبانان و مأموران حراست | مأموران پلیس راه‌آهن و پایانه‌های مسافربری</t>
+          <t>مأموران انتظامات و حفاظت دادگاه | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران گشت پلیس و کلانتری | مددکاران قضایی و متخصصان اصلاح و تربیت | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حقوق و امور حکومتی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | روان‌شناسی | رایانه و الکترونیک | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مأموران زندان و بازداشتگاه | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | تکنسین‌های علوم جنایی و آزمایشگاه تشخیص هویت | کارشناسان، بازرسان و تحلیل‌گران بررسی تقلب و کلاهبرداری | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | مأموران گشت پلیس و کلانتری</t>
+          <t>مأموران زندان و بازداشتگاه | سرپرستان رده‌اول پلیس و کارآگاهان | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | ماموران گشت پلیس و کلانتری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حقوق و امور حکومتی | امور دفتری و اداری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | آموزش و تدریس</t>
+          <t>قانون و دولت | اداری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مأموران پزشک قانونی و ثبت فوت | کارآگاهان و بازرسان جنایی | تحلیل‌گران فارنزیک دیجیتال و جرایم سایبری | تکنسین‌های علوم جنایی و آزمایشگاه تشخیص هویت | کارشناسان، بازرسان و تحلیل‌گران بررسی تقلب و کلاهبرداری | تحلیل‌گران داده‌ها و اطلاعات امنیتی | مأموران گشت پلیس و کلانتری</t>
+          <t>پزشکان قانونی و بازرسان مرگ مشکوک | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران داده‌ها و اطلاعات امنیتی | ماموران گشت پلیس و کلانتری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و امور حکومتی | ایمنی و امنیت عمومی | رایانه و الکترونیک | ارتباطات و رسانه | مخابرات و ارتباطات</t>
+          <t>زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | ارتباطات و رسانه | مخابرات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری BI | کارآگاهان و بازرسان جنایی | تحلیل‌گران فارنزیک دیجیتال و جرایم سایبری | کارشناسان، بازرسان و تحلیل‌گران بررسی تقلب و کلاهبرداری | تحلیل‌گران امنیت اطلاعات | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارشناسان تخصصی مدیریت حراست</t>
+          <t>تحلیل‌گران هوش تجاری | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران امنیت اطلاعات | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارشناسان مدیریت حراست و امنیت فیزیکی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
